--- a/documents/china_southern_air/充氧类水生动物货物收运检查单.xlsx
+++ b/documents/china_southern_air/充氧类水生动物货物收运检查单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -177,11 +177,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="43">
     <font>
@@ -1162,10 +1163,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">

--- a/documents/china_southern_air/充氧类水生动物货物收运检查单.xlsx
+++ b/documents/china_southern_air/充氧类水生动物货物收运检查单.xlsx
@@ -27,40 +27,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>陈志超</author>
-  </authors>
-  <commentList>
-    <comment ref="C16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-件数</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
   <si>
     <t>充氧类水生动物/水产品货物收运检查单（冰、鲜）</t>
   </si>
@@ -165,9 +133,6 @@
   </si>
   <si>
     <t>检查人签字：</t>
-  </si>
-  <si>
-    <t>（不是货代填写，这里不用管）</t>
   </si>
   <si>
     <t xml:space="preserve">                       深圳市薛航物流有限公司</t>
@@ -184,7 +149,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,12 +228,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="方正黑体_GBK"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <name val="方正仿宋_GBK"/>
@@ -291,13 +250,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="方正仿宋_GBK"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="14"/>
       <name val="方正仿宋_GBK"/>
       <charset val="134"/>
@@ -306,13 +258,6 @@
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="方正仿宋_GBK"/>
       <charset val="134"/>
     </font>
     <font>
@@ -458,17 +403,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -948,137 +882,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1157,94 +1091,85 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1628,138 +1553,138 @@
         <v>5</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="31" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="31"/>
-      <c r="I4" s="30" t="s">
+      <c r="H4" s="26"/>
+      <c r="I4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="32"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="26" customHeight="1" spans="1:10">
       <c r="A5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="31"/>
-      <c r="I5" s="30" t="s">
+      <c r="H5" s="26"/>
+      <c r="I5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="32"/>
+      <c r="J5" s="30"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35" t="s">
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="33" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="J7" s="36" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="I8" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="J8" s="36" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="38" t="s">
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="I9" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="36" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38" t="s">
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="38" t="s">
+      <c r="J10" s="36" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1775,149 +1700,147 @@
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
       <c r="I11" s="22"/>
-      <c r="J11" s="39"/>
+      <c r="J11" s="37"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="38" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="38" t="s">
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="38" t="s">
+      <c r="I13" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="38" t="s">
+      <c r="J13" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="38" t="s">
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="38" t="s">
+      <c r="I14" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="38" t="s">
+      <c r="J14" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="41" customHeight="1" spans="1:10">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="42" t="s">
+      <c r="I15" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="42" t="s">
+      <c r="J15" s="40" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.5" customHeight="1" spans="1:10">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="45">
+      <c r="B16" s="42"/>
+      <c r="C16" s="43">
         <v>3</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48" t="s">
+      <c r="E16" s="45"/>
+      <c r="F16" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="45"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="43"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="28" customHeight="1" spans="1:10">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50" t="s">
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="50" t="s">
+      <c r="I17" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="50" t="s">
+      <c r="J17" s="48" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="42" customHeight="1" spans="1:10">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="53" t="s">
+      <c r="B18" s="50"/>
+      <c r="C18" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="52" t="s">
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="52"/>
-      <c r="H18" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="54"/>
-      <c r="J18" s="55"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -1956,7 +1879,6 @@
   <pageMargins left="0.751388888888889" right="0.156944444444444" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1988,7 +1910,7 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="26" customHeight="1" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
